--- a/Kaasuu.xlsx
+++ b/Kaasuu.xlsx
@@ -24,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>Lak k.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Maqaa miseensotaa</t>
   </si>
@@ -432,280 +429,208 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="1">
+      <c r="B16" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="1">
+      <c r="B22" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1">
+      <c r="B23" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="B24" s="1">
         <v>3000</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:C69">
-    <sortCondition descending="1" ref="C2"/>
+    <sortCondition descending="1" ref="B2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Kaasuu.xlsx
+++ b/Kaasuu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Maqaa miseensotaa</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Hamma Maallaqaa</t>
   </si>
   <si>
-    <t>Asheetuu Badhaadhaa</t>
-  </si>
-  <si>
     <t>Gabbisaa Katamaa</t>
   </si>
   <si>
@@ -48,12 +45,6 @@
   </si>
   <si>
     <t>Boggaalee Qajeelaa</t>
-  </si>
-  <si>
-    <t>Tigisti  Mangashaa</t>
-  </si>
-  <si>
-    <t>Daraartu Baqqalaa</t>
   </si>
   <si>
     <t>Daraartu Baqalaa</t>
@@ -429,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.5546875" bestFit="1" customWidth="1"/>
@@ -529,7 +520,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -553,7 +544,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -577,7 +568,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -585,7 +576,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -593,7 +584,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -601,30 +592,6 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="1">
         <v>3000</v>
       </c>
     </row>

--- a/Kaasuu.xlsx
+++ b/Kaasuu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Maqaa miseensotaa</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Boggaalee Qajeelaa</t>
   </si>
   <si>
-    <t>Daraartu Baqalaa</t>
-  </si>
-  <si>
     <t>Dirribaa Taammiruu</t>
   </si>
   <si>
@@ -90,6 +87,12 @@
   </si>
   <si>
     <t>Haftaamuu Biraanuu</t>
+  </si>
+  <si>
+    <t>Darartuu Baqqalaa1</t>
+  </si>
+  <si>
+    <t>Daraartuu Baqqalaa2</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.5546875" bestFit="1" customWidth="1"/>
@@ -477,7 +480,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
         <v>3000</v>
@@ -485,7 +488,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>3000</v>
@@ -493,7 +496,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>3000</v>
@@ -501,7 +504,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>3000</v>
@@ -509,7 +512,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>3000</v>
@@ -517,7 +520,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>1500</v>
@@ -525,7 +528,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>3000</v>
@@ -533,7 +536,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>3000</v>
@@ -541,7 +544,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>3000</v>
@@ -549,7 +552,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
         <v>3000</v>
@@ -557,7 +560,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
         <v>3000</v>
@@ -565,7 +568,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>1500</v>
@@ -573,7 +576,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>1500</v>
@@ -581,7 +584,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>1500</v>
@@ -589,9 +592,17 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B22" s="1">
         <v>3000</v>
       </c>
     </row>

--- a/Kaasuu.xlsx
+++ b/Kaasuu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Maqaa miseensotaa</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Alamuu Kaasuu</t>
   </si>
   <si>
-    <t>Lataa Miliyoon</t>
-  </si>
-  <si>
     <t>Fiqaaduu Ayiluu</t>
   </si>
   <si>
@@ -77,15 +74,6 @@
     <t>Mubarik Sharing</t>
   </si>
   <si>
-    <t>Mammee Gisachoo</t>
-  </si>
-  <si>
-    <t>Baqqalaa Lataa</t>
-  </si>
-  <si>
-    <t>Dawwitee Tolasaa</t>
-  </si>
-  <si>
     <t>Haftaamuu Biraanuu</t>
   </si>
   <si>
@@ -93,6 +81,12 @@
   </si>
   <si>
     <t>Daraartuu Baqqalaa2</t>
+  </si>
+  <si>
+    <t>Mammee Gisachoo fi Baqqalaa Lataa</t>
+  </si>
+  <si>
+    <t>Lataa Miliyoon fi Dawwitee Tolasaa</t>
   </si>
 </sst>
 </file>
@@ -423,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.5546875" bestFit="1" customWidth="1"/>
@@ -480,7 +474,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1">
         <v>3000</v>
@@ -520,15 +514,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>3000</v>
@@ -536,7 +530,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>3000</v>
@@ -544,7 +538,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>3000</v>
@@ -552,7 +546,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>3000</v>
@@ -560,7 +554,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
         <v>3000</v>
@@ -568,41 +562,25 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
         <v>3000</v>
       </c>
     </row>

--- a/Kaasuu.xlsx
+++ b/Kaasuu.xlsx
@@ -24,15 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Maqaa miseensotaa</t>
   </si>
   <si>
     <t>Hamma Maallaqaa</t>
-  </si>
-  <si>
-    <t>Gabbisaa Katamaa</t>
   </si>
   <si>
     <t>Kaasaa Gaaddisaa</t>
@@ -417,11 +414,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -466,7 +463,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
         <v>3000</v>
@@ -474,7 +471,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>3000</v>
@@ -506,7 +503,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1">
         <v>3000</v>
@@ -514,7 +511,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>3000</v>
@@ -554,7 +551,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1">
         <v>3000</v>
@@ -562,7 +559,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1">
         <v>3000</v>
@@ -573,14 +570,6 @@
         <v>16</v>
       </c>
       <c r="B19" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1">
         <v>3000</v>
       </c>
     </row>
